--- a/CPRD Raw Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>496.508</v>
+        <v>727.829</v>
       </c>
       <c r="D2">
-        <v>8.795</v>
+        <v>19.474</v>
       </c>
       <c r="E2">
-        <v>2.966</v>
+        <v>4.413</v>
       </c>
       <c r="F2">
-        <v>0.094</v>
+        <v>0.14</v>
       </c>
       <c r="G2">
-        <v>490.787</v>
+        <v>719.327</v>
       </c>
       <c r="H2">
-        <v>502.412</v>
+        <v>736.626</v>
       </c>
       <c r="I2">
-        <v>490.353</v>
+        <v>718.954</v>
       </c>
       <c r="J2">
-        <v>502.436</v>
+        <v>736.765</v>
       </c>
       <c r="K2">
-        <v>490.672</v>
+        <v>719.0410000000001</v>
       </c>
       <c r="L2">
-        <v>502.754</v>
+        <v>736.852</v>
       </c>
     </row>
     <row r="3">
@@ -466,274 +466,114 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>421.98</v>
+        <v>622.9880000000001</v>
       </c>
       <c r="D3">
-        <v>12.914</v>
+        <v>28.962</v>
       </c>
       <c r="E3">
-        <v>3.594</v>
+        <v>5.382</v>
       </c>
       <c r="F3">
-        <v>0.114</v>
+        <v>0.17</v>
       </c>
       <c r="G3">
-        <v>414.868</v>
+        <v>612.297</v>
       </c>
       <c r="H3">
-        <v>428.954</v>
+        <v>633.393</v>
       </c>
       <c r="I3">
-        <v>415.122</v>
+        <v>612.381</v>
       </c>
       <c r="J3">
-        <v>428.916</v>
+        <v>633.3200000000001</v>
       </c>
       <c r="K3">
-        <v>414.975</v>
+        <v>612.513</v>
       </c>
       <c r="L3">
-        <v>428.769</v>
+        <v>633.452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>476.268</v>
+        <v>747.963</v>
       </c>
       <c r="D4">
-        <v>8.33</v>
+        <v>23.174</v>
       </c>
       <c r="E4">
-        <v>2.886</v>
+        <v>4.814</v>
       </c>
       <c r="F4">
-        <v>0.091</v>
+        <v>0.152</v>
       </c>
       <c r="G4">
-        <v>470.693</v>
+        <v>738.553</v>
       </c>
       <c r="H4">
-        <v>482.007</v>
+        <v>757.424</v>
       </c>
       <c r="I4">
-        <v>470.337</v>
+        <v>738.603</v>
       </c>
       <c r="J4">
-        <v>482.025</v>
+        <v>757.597</v>
       </c>
       <c r="K4">
-        <v>470.594</v>
+        <v>738.355</v>
       </c>
       <c r="L4">
-        <v>482.281</v>
+        <v>757.349</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>408.032</v>
+        <v>627.665</v>
       </c>
       <c r="D5">
-        <v>12.257</v>
+        <v>30.861</v>
       </c>
       <c r="E5">
-        <v>3.501</v>
+        <v>5.555</v>
       </c>
       <c r="F5">
-        <v>0.111</v>
+        <v>0.176</v>
       </c>
       <c r="G5">
-        <v>401.075</v>
+        <v>617.186</v>
       </c>
       <c r="H5">
-        <v>414.798</v>
+        <v>638.962</v>
       </c>
       <c r="I5">
-        <v>401.35</v>
+        <v>616.597</v>
       </c>
       <c r="J5">
-        <v>414.737</v>
+        <v>638.846</v>
       </c>
       <c r="K5">
-        <v>401.232</v>
+        <v>616.893</v>
       </c>
       <c r="L5">
-        <v>414.618</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>510.553</v>
-      </c>
-      <c r="D6">
-        <v>9.113</v>
-      </c>
-      <c r="E6">
-        <v>3.019</v>
-      </c>
-      <c r="F6">
-        <v>0.095</v>
-      </c>
-      <c r="G6">
-        <v>504.543</v>
-      </c>
-      <c r="H6">
-        <v>516.376</v>
-      </c>
-      <c r="I6">
-        <v>504.486</v>
-      </c>
-      <c r="J6">
-        <v>516.403</v>
-      </c>
-      <c r="K6">
-        <v>504.61</v>
-      </c>
-      <c r="L6">
-        <v>516.527</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>425.128</v>
-      </c>
-      <c r="D7">
-        <v>13.558</v>
-      </c>
-      <c r="E7">
-        <v>3.682</v>
-      </c>
-      <c r="F7">
-        <v>0.116</v>
-      </c>
-      <c r="G7">
-        <v>418.316</v>
-      </c>
-      <c r="H7">
-        <v>432.75</v>
-      </c>
-      <c r="I7">
-        <v>418.285</v>
-      </c>
-      <c r="J7">
-        <v>432.725</v>
-      </c>
-      <c r="K7">
-        <v>417.936</v>
-      </c>
-      <c r="L7">
-        <v>432.376</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>489.926</v>
-      </c>
-      <c r="D8">
-        <v>8.691000000000001</v>
-      </c>
-      <c r="E8">
-        <v>2.948</v>
-      </c>
-      <c r="F8">
-        <v>0.093</v>
-      </c>
-      <c r="G8">
-        <v>484.053</v>
-      </c>
-      <c r="H8">
-        <v>495.609</v>
-      </c>
-      <c r="I8">
-        <v>483.829</v>
-      </c>
-      <c r="J8">
-        <v>495.603</v>
-      </c>
-      <c r="K8">
-        <v>484.154</v>
-      </c>
-      <c r="L8">
-        <v>495.927</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>411.078</v>
-      </c>
-      <c r="D9">
-        <v>12.943</v>
-      </c>
-      <c r="E9">
-        <v>3.598</v>
-      </c>
-      <c r="F9">
-        <v>0.114</v>
-      </c>
-      <c r="G9">
-        <v>404.397</v>
-      </c>
-      <c r="H9">
-        <v>418.499</v>
-      </c>
-      <c r="I9">
-        <v>404.493</v>
-      </c>
-      <c r="J9">
-        <v>418.603</v>
-      </c>
-      <c r="K9">
-        <v>403.923</v>
-      </c>
-      <c r="L9">
-        <v>418.033</v>
+        <v>639.141</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>727.829</v>
+        <v>934.576</v>
       </c>
       <c r="D2">
-        <v>19.474</v>
+        <v>66.875</v>
       </c>
       <c r="E2">
-        <v>4.413</v>
+        <v>8.178000000000001</v>
       </c>
       <c r="F2">
-        <v>0.14</v>
+        <v>0.259</v>
       </c>
       <c r="G2">
-        <v>719.327</v>
+        <v>918.444</v>
       </c>
       <c r="H2">
-        <v>736.626</v>
+        <v>950.5</v>
       </c>
       <c r="I2">
-        <v>718.954</v>
+        <v>918.616</v>
       </c>
       <c r="J2">
-        <v>736.765</v>
+        <v>950.5069999999999</v>
       </c>
       <c r="K2">
-        <v>719.0410000000001</v>
+        <v>918.542</v>
       </c>
       <c r="L2">
-        <v>736.852</v>
+        <v>950.432</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>622.9880000000001</v>
+        <v>431.219</v>
       </c>
       <c r="D3">
-        <v>28.962</v>
+        <v>61.372</v>
       </c>
       <c r="E3">
-        <v>5.382</v>
+        <v>7.834</v>
       </c>
       <c r="F3">
-        <v>0.17</v>
+        <v>0.248</v>
       </c>
       <c r="G3">
-        <v>612.297</v>
+        <v>415.663</v>
       </c>
       <c r="H3">
-        <v>633.393</v>
+        <v>446.372</v>
       </c>
       <c r="I3">
-        <v>612.381</v>
+        <v>415.534</v>
       </c>
       <c r="J3">
-        <v>633.3200000000001</v>
+        <v>446.404</v>
       </c>
       <c r="K3">
-        <v>612.513</v>
+        <v>415.832</v>
       </c>
       <c r="L3">
-        <v>633.452</v>
+        <v>446.702</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>747.963</v>
+        <v>1043.566</v>
       </c>
       <c r="D4">
-        <v>23.174</v>
+        <v>76.947</v>
       </c>
       <c r="E4">
-        <v>4.814</v>
+        <v>8.772</v>
       </c>
       <c r="F4">
-        <v>0.152</v>
+        <v>0.277</v>
       </c>
       <c r="G4">
-        <v>738.553</v>
+        <v>1026.441</v>
       </c>
       <c r="H4">
-        <v>757.424</v>
+        <v>1060.826</v>
       </c>
       <c r="I4">
-        <v>738.603</v>
+        <v>1026.713</v>
       </c>
       <c r="J4">
-        <v>757.597</v>
+        <v>1061.19</v>
       </c>
       <c r="K4">
-        <v>738.355</v>
+        <v>1026.01</v>
       </c>
       <c r="L4">
-        <v>757.349</v>
+        <v>1060.487</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>627.665</v>
+        <v>461.309</v>
       </c>
       <c r="D5">
-        <v>30.861</v>
+        <v>66.547</v>
       </c>
       <c r="E5">
-        <v>5.555</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="F5">
-        <v>0.176</v>
+        <v>0.258</v>
       </c>
       <c r="G5">
-        <v>617.186</v>
+        <v>445.605</v>
       </c>
       <c r="H5">
-        <v>638.962</v>
+        <v>477.583</v>
       </c>
       <c r="I5">
-        <v>616.597</v>
+        <v>444.834</v>
       </c>
       <c r="J5">
-        <v>638.846</v>
+        <v>476.975</v>
       </c>
       <c r="K5">
-        <v>616.893</v>
+        <v>445.927</v>
       </c>
       <c r="L5">
-        <v>639.141</v>
+        <v>478.068</v>
       </c>
     </row>
   </sheetData>
